--- a/AAII_Financials/Yearly/PINXY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PINXY_YR_FIN.xlsx
@@ -714,7 +714,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>89224000</v>
+        <v>89129000</v>
       </c>
       <c r="E8" s="3">
         <v>79671500</v>
@@ -780,7 +780,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>12942500</v>
+        <v>12847600</v>
       </c>
       <c r="E10" s="3">
         <v>11128600</v>
@@ -894,7 +894,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>469900</v>
+        <v>375000</v>
       </c>
       <c r="E14" s="3">
         <v>245400</v>
@@ -1005,7 +1005,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11286000</v>
+        <v>11191100</v>
       </c>
       <c r="E18" s="3">
         <v>9932600</v>
@@ -1086,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>11612300</v>
+        <v>11517400</v>
       </c>
       <c r="E21" s="3">
         <v>10280700</v>
